--- a/Assets/Data/Excel/AssetPath.xlsx
+++ b/Assets/Data/Excel/AssetPath.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
   <si>
     <r>
       <rPr>
@@ -102,6 +102,7 @@
         <sz val="10"/>
         <rFont val="Arial Unicode MS"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">资源</t>
     </r>
@@ -110,6 +111,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">id</t>
     </r>
@@ -120,6 +122,7 @@
         <sz val="10"/>
         <rFont val="Arial Unicode MS"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">资源路径</t>
     </r>
@@ -128,6 +131,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Assets/</t>
     </r>
@@ -136,12 +140,28 @@
         <sz val="10"/>
         <rFont val="Arial Unicode MS"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">开头</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">s</t>
+    <t xml:space="preserve">AssetPath</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assets/Data/TXT/AssetPath.txt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BuildingData</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assets/Data/TXT/BuildingData.txt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BuildingLevelData</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assets/Data/TXT/BuildingLevelData.txt</t>
   </si>
 </sst>
 </file>
@@ -156,6 +176,7 @@
       <sz val="10"/>
       <name val="Arial Unicode MS"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -188,6 +209,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -232,8 +254,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -241,7 +267,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -371,52 +397,84 @@
   <dimension ref="A1:F10"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="21.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="20.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="42.13"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="16.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="16.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>9</v>
       </c>
     </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F10" s="2" t="s">
-        <v>10</v>
-      </c>
+      <c r="F10" s="3"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/Assets/Data/Excel/AssetPath.xlsx
+++ b/Assets/Data/Excel/AssetPath.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
   <si>
     <r>
       <rPr>
@@ -144,6 +144,9 @@
       </rPr>
       <t xml:space="preserve">开头</t>
     </r>
+  </si>
+  <si>
+    <t xml:space="preserve">ss</t>
   </si>
   <si>
     <t xml:space="preserve">AssetPath</t>
@@ -441,36 +444,45 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>10</v>
+      </c>
       <c r="B4" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="1" t="n">
         <v>2</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
+        <v>10</v>
+      </c>
       <c r="B6" s="1" t="n">
         <v>3</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/Assets/Data/Excel/AssetPath.xlsx
+++ b/Assets/Data/Excel/AssetPath.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
   <si>
     <r>
       <rPr>
@@ -146,9 +146,6 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">ss</t>
-  </si>
-  <si>
     <t xml:space="preserve">AssetPath</t>
   </si>
   <si>
@@ -165,6 +162,12 @@
   </si>
   <si>
     <t xml:space="preserve">Assets/Data/TXT/BuildingLevelData.txt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assets/Res/Prefab/jidi.prefab</t>
   </si>
 </sst>
 </file>
@@ -397,7 +400,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="20.89"/>
@@ -444,49 +447,58 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
-        <v>10</v>
-      </c>
+      <c r="A4" s="1"/>
       <c r="B4" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>12</v>
-      </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
-        <v>10</v>
-      </c>
+      <c r="A5" s="1"/>
       <c r="B5" s="1" t="n">
         <v>2</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>14</v>
-      </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
-        <v>10</v>
-      </c>
+      <c r="A6" s="1"/>
       <c r="B6" s="1" t="n">
         <v>3</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="1" t="s">
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F10" s="3"/>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="1" t="n">
+        <v>101</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="1" t="n">
+        <v>102</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/Assets/Data/Excel/AssetPath.xlsx
+++ b/Assets/Data/Excel/AssetPath.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
   <si>
     <r>
       <rPr>
@@ -400,7 +400,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="20.89"/>
@@ -486,17 +486,29 @@
       <c r="A7" s="1" t="s">
         <v>16</v>
       </c>
+      <c r="B7" s="1"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="1" t="n">
+      <c r="A8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="1"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="1" t="n">
         <v>101</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D10" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="1" t="n">
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="1" t="n">
         <v>102</v>
       </c>
     </row>

--- a/Assets/Data/Excel/AssetPath.xlsx
+++ b/Assets/Data/Excel/AssetPath.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="20">
   <si>
     <r>
       <rPr>
@@ -165,6 +165,12 @@
   </si>
   <si>
     <t xml:space="preserve">#</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PoolConfig</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assets/Data/TXT/PoolConfig.txt</t>
   </si>
   <si>
     <t xml:space="preserve">Assets/Res/Prefab/jidi.prefab</t>
@@ -486,7 +492,15 @@
       <c r="A7" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="1"/>
+      <c r="B7" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
@@ -504,7 +518,7 @@
         <v>101</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">

--- a/Assets/Data/Excel/AssetPath.xlsx
+++ b/Assets/Data/Excel/AssetPath.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
   <si>
     <r>
       <rPr>
@@ -174,6 +174,9 @@
   </si>
   <si>
     <t xml:space="preserve">Assets/Res/Prefab/jidi.prefab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assets/Res/Prefab/Cylinder.prefab</t>
   </si>
 </sst>
 </file>
@@ -525,6 +528,9 @@
       <c r="B11" s="1" t="n">
         <v>102</v>
       </c>
+      <c r="D11" s="1" t="s">
+        <v>20</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/Assets/Data/Excel/AssetPath.xlsx
+++ b/Assets/Data/Excel/AssetPath.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="27">
   <si>
     <r>
       <rPr>
@@ -173,10 +173,28 @@
     <t xml:space="preserve">Assets/Data/TXT/PoolConfig.txt</t>
   </si>
   <si>
+    <t xml:space="preserve">UnitData</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assets/Data/TXT/UnitData.txt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UnitLevelData</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assets/Data/TXT/UnitLevelData.txt</t>
+  </si>
+  <si>
     <t xml:space="preserve">Assets/Res/Prefab/jidi.prefab</t>
   </si>
   <si>
     <t xml:space="preserve">Assets/Res/Prefab/Cylinder.prefab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assets/Res/Prefab/独眼.prefab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assets/Res/Prefab/Indicator.prefab</t>
   </si>
 </sst>
 </file>
@@ -409,7 +427,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="20.89"/>
@@ -506,30 +524,121 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="1"/>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
+      <c r="B10" s="1"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="1" t="n">
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B12" s="1" t="n">
         <v>101</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="1" t="n">
+      <c r="D12" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B13" s="1" t="n">
         <v>102</v>
       </c>
-      <c r="D11" s="1" t="s">
-        <v>20</v>
+      <c r="D13" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B14" s="1" t="n">
+        <v>103</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B15" s="1" t="n">
+        <v>104</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" s="1"/>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B17" s="1" t="n">
+        <v>1111</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B18" s="1" t="n">
+        <v>2222</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B19" s="1" t="n">
+        <v>3333</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B20" s="1" t="n">
+        <v>109</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="0" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="0" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
